--- a/Homework7/Homework7d_FSM_transition_table_and_implication_chart_template.xlsx
+++ b/Homework7/Homework7d_FSM_transition_table_and_implication_chart_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\visha\Documents\UCSD\ECE-111-Verilog\Homework\summer2024\Homework7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jaspe\repositories\ECE 111 Lab HW\Homework7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1730D1-2E72-442D-9042-E0BF39FC561B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF6F924-43E4-46DD-AEBA-6DDDB56D9EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14563" yWindow="0" windowWidth="14923" windowHeight="11623" xr2:uid="{97438D8C-423D-45C7-895F-233AC13CE315}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{97438D8C-423D-45C7-895F-233AC13CE315}"/>
   </bookViews>
   <sheets>
     <sheet name="Vending Machine" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="23">
   <si>
     <t>D=0, N=0</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Vending Machine Implication Chart</t>
+  </si>
+  <si>
+    <t>c</t>
   </si>
 </sst>
 </file>
@@ -278,8 +281,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6560212" y="2775857"/>
-          <a:ext cx="675950" cy="4365152"/>
+          <a:off x="6161627" y="2857500"/>
+          <a:ext cx="630942" cy="4490338"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -296,8 +299,8 @@
       <xdr:rowOff>177639</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>623325</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>5666</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>107951</xdr:rowOff>
     </xdr:to>
@@ -322,8 +325,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7231757" y="3323610"/>
-          <a:ext cx="679554" cy="3816512"/>
+          <a:off x="6797689" y="3416139"/>
+          <a:ext cx="627952" cy="3930812"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -334,8 +337,8 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>631268</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>4084</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>164612</xdr:rowOff>
     </xdr:from>
@@ -366,8 +369,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7919254" y="3865755"/>
-          <a:ext cx="679554" cy="3271296"/>
+          <a:off x="7411603" y="3974612"/>
+          <a:ext cx="608588" cy="3369268"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2903,13 +2906,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>84158</xdr:colOff>
+      <xdr:colOff>113465</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>91611</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>430871</xdr:colOff>
+      <xdr:colOff>460178</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>80026</xdr:rowOff>
     </xdr:to>
@@ -2926,8 +2929,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6719001" y="3977811"/>
-          <a:ext cx="346713" cy="358529"/>
+          <a:off x="6341987" y="4092111"/>
+          <a:ext cx="346713" cy="369415"/>
           <a:chOff x="1199213" y="2628627"/>
           <a:chExt cx="346713" cy="358529"/>
         </a:xfrm>
@@ -2974,6 +2977,4440 @@
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                 <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0361C93-7770-C72B-433A-B3BBED86EB85}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>586887</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>189161</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>500779</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>24848</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15E928CE-B235-CF5C-9E26-A8E77E5B99D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6202496" y="3427661"/>
+          <a:ext cx="526805" cy="597687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S1-S3</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1"/>
+            <a:t>S3-S6</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1"/>
+            <a:t>S2-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S7</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>94415</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>72561</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>441128</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>60976</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="76" name="Group 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46E9E062-8C8E-48A6-B24A-E7FC61C56E91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6322937" y="4644561"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="77" name="Straight Connector 76">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF1BDEBB-2D50-C8C7-4D90-7923B11A29B1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="78" name="Straight Connector 77">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5703206-BF0B-2FCB-2766-CC53F4B76699}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>84890</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>24936</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>431603</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>13351</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="79" name="Group 78">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57B97393-B9FF-410C-8C91-E35E7AB336ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6313412" y="5739936"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="80" name="Straight Connector 79">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16108B78-AAF5-09BD-E340-2517314551A4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="81" name="Straight Connector 80">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{384D1F75-8050-3F90-D3FF-BD453467C171}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>84890</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>34461</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>431603</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>22876</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="82" name="Group 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EB71448-1483-46FB-A26C-2F589815330A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6313412" y="6320961"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="83" name="Straight Connector 82">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C544D9B2-CFA1-5A6D-AFF1-FE0359647EDE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="84" name="Straight Connector 83">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE0433D7-DF12-6DEE-C6AC-64B94944AA85}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>103940</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>186861</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>450653</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>175276</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="85" name="Group 84">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E65ACB79-F751-41AA-99DB-C224BA63A483}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6332462" y="6854361"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="86" name="Straight Connector 85">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B0E61F1-C018-B233-6353-D862F013DD43}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="87" name="Straight Connector 86">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87980807-82D7-DE4F-19D4-75D35B35B0DC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>113465</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>53511</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>460178</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>41926</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="88" name="Group 87">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B11E685C-2341-4E1C-B4FF-04C4411B995C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6954900" y="4054011"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="89" name="Straight Connector 88">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46AF506C-A174-D716-5989-58F0E22408A3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="90" name="Straight Connector 89">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3C64057-4A8C-74E4-D5E0-9E063ACB9473}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>94415</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>91611</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>441128</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>80026</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="91" name="Group 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D335DA8-C1BC-4AB2-84D4-C88D8920E87F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="7548763" y="4092111"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="92" name="Straight Connector 91">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE214661-7DBB-EBFE-3D7B-D4B7B374AABA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="93" name="Straight Connector 92">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DFBC2F8-9762-870A-A5BD-97E714B3AB6D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>103940</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>53511</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>450653</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>41926</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="94" name="Group 93">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2BC7F49-572A-CF95-B27C-223DD4C6D202}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6945375" y="4625511"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="95" name="Straight Connector 94">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63EB380F-623F-D4BF-44C7-B72DB3E31746}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="96" name="Straight Connector 95">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BBE80C0-5EE6-2710-1C4D-AE51ADAA2A01}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>122990</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>15411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>469703</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3826</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="97" name="Group 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B698976F-FC97-492A-8F68-E1BA55E5F502}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6964425" y="5730411"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="98" name="Straight Connector 97">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC611554-77C1-B2D3-F517-47F2726C0114}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="99" name="Straight Connector 98">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A67E5B4E-B1A9-A6BE-1EFF-30CD9086B79A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>122990</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>5886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>469703</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>184801</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="100" name="Group 99">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98272974-291B-4548-AEDE-3E3196DCE54C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6964425" y="6292386"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="101" name="Straight Connector 100">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D80443D9-9F67-78DA-B267-99344A26B50E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="102" name="Straight Connector 101">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47270A13-B705-2694-A6B0-4B0B686F3861}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>132515</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>186861</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>479228</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>175276</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="103" name="Group 102">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BAABF0A-C050-494D-87AC-DFCC8A9F6AEE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6973950" y="6854361"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="104" name="Straight Connector 103">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3473FBF7-B278-9E68-F92F-655FCE3BED7E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="105" name="Straight Connector 104">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E543DDDF-21BD-83B3-48D7-72E26CB4EF32}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>103940</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>15411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>450653</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>3826</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="106" name="Group 105">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43053F65-FE85-4D33-B8F7-075D85BB45EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="7558288" y="4587411"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="107" name="Straight Connector 106">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85936223-A83C-1C16-8C93-819CE0A74AB9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="108" name="Straight Connector 107">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71270690-EEFC-DC16-907E-4CD7777A439D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>94415</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>24936</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>441128</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>13351</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="109" name="Group 108">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F92C217-FFC0-4BE2-B2CC-15BE6C565A8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="7548763" y="5739936"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="110" name="Straight Connector 109">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A71C92E-61D9-F0FB-633C-4DB3AE3B5684}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="111" name="Straight Connector 110">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D4402F0-5F6A-F4A2-BA9B-A142CDD9DC52}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>151565</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>158286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>498278</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>146701</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="112" name="Group 111">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDDDAE2B-47D4-41FA-8CDA-66DFDC0FB476}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="7605913" y="6254286"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="113" name="Straight Connector 112">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B21BC5D8-CF9C-DA63-1E8F-5BA470FEB0CA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="114" name="Straight Connector 113">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68E90B23-E0EF-719F-3152-3F053C2D6E1F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>142040</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>5886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>488753</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>184801</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="115" name="Group 114">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25711EBD-24DA-4C74-97DE-DFC53A74FBEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="7596388" y="6863886"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="116" name="Straight Connector 115">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B21AD370-BF8D-FE73-F329-38E8F2B435DE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="117" name="Straight Connector 116">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{389549D8-5633-A23F-59B2-7A64EA7F29CD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>151565</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>24936</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>498278</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>13351</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="118" name="Group 117">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8F5E253-986D-49E4-BB68-2F7420919856}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="8218826" y="5168436"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="119" name="Straight Connector 118">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18A79582-75F8-FDCB-EB03-DBF8066BC245}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="120" name="Straight Connector 119">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94F84D52-F400-3B30-59AC-89CB04A1C1CF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>170615</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>15411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>517328</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>3826</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="121" name="Group 120">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41B834A6-04E3-4DE5-9B4C-F3AD9795399B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="8850789" y="5158911"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="122" name="Straight Connector 121">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77B6F4DF-C331-14F8-848F-6E11D9927E53}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="123" name="Straight Connector 122">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2997DDB4-32BF-95D2-CCAE-FF4C4BDFB2C9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>208715</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>34461</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>555428</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>22876</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="124" name="Group 123">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19459C76-1A6C-4A7E-8887-BD27C20CAABB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="9501802" y="5749461"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="125" name="Straight Connector 124">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41241D02-BAF2-003A-2D3A-D84E93ED4428}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="126" name="Straight Connector 125">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{607C5DF7-AD77-0C81-1E51-8CBA137B0F20}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>218240</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>15411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>564953</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>3826</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="127" name="Group 126">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A766549-A0E9-4727-9846-6568E513F710}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="9511327" y="6301911"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="128" name="Straight Connector 127">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BB731D8-6477-356C-A23B-BE515C1E4A84}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="129" name="Straight Connector 128">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F2EC0F6-1A46-0BF5-D91F-D1216F9C4812}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>199190</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>186861</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>545903</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>175276</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="130" name="Group 129">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{247D2CF0-B908-41EC-9E5D-F9741B73CF9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="9492277" y="6854361"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="131" name="Straight Connector 130">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1FF046-C143-AC53-89F7-780C84E4975C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="132" name="Straight Connector 131">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DC0FC9B-87E6-DCFC-4A76-4F2FE0E67C9A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>570866</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>140805</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>484758</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>166992</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="133" name="TextBox 132">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD4BB98C-53B9-434E-BF1B-745B8EFB6344}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6186475" y="5093805"/>
+          <a:ext cx="526805" cy="597687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S1-S6</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1"/>
+            <a:t>S3-S8</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1"/>
+            <a:t>S2-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S9</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>43548</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>184191</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>570353</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19878</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="134" name="TextBox 133">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6B763C8-1C07-40DB-86B1-C05C559D9323}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6884983" y="3422691"/>
+          <a:ext cx="526805" cy="597687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S2-S3</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1"/>
+            <a:t>S4-S6</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1"/>
+            <a:t>S5-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S7</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38579</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>146091</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>565384</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>172278</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="135" name="TextBox 134">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E7D5637-16A0-4CC2-83BC-C96DFD711976}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6880014" y="5099091"/>
+          <a:ext cx="526805" cy="597687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S2-S6</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1"/>
+            <a:t>S4-S8</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1"/>
+            <a:t>S5-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S9</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>41892</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>149404</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>568697</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>175591</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="136" name="TextBox 135">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78B6B90A-9B5B-4550-B648-13A8D9037737}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7496240" y="5102404"/>
+          <a:ext cx="526805" cy="597687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S3-S6</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1"/>
+            <a:t>S6-S8</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1"/>
+            <a:t>S7-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S9</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>86618</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>127869</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>510</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>149087</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="137" name="TextBox 136">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB1C18A4-04B9-4B5B-8336-CEAEC60FE5A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8153879" y="4699869"/>
+          <a:ext cx="526805" cy="211718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S1-S3</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>81649</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>106335</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>608454</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>127553</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="138" name="TextBox 137">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09752A3A-B216-4E67-92E3-52E9658F1170}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8148910" y="5821335"/>
+          <a:ext cx="526805" cy="211718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S1-S1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>84962</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>43387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>611767</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>64605</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="139" name="TextBox 138">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90C54787-9B33-4D89-956A-A8F79217B894}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8152223" y="6329887"/>
+          <a:ext cx="526805" cy="211718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S1-S1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>51156</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>52611</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>577961</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>73829</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="140" name="TextBox 139">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFF24300-3BFF-4DAB-A997-ABB1D885DFC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8118417" y="6910611"/>
+          <a:ext cx="526805" cy="211718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S1-S3</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>60114</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>84799</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>586919</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>106017</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="141" name="TextBox 140">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2F17A75-19DA-47AE-BECA-9D9AC54F4AB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8740288" y="5799799"/>
+          <a:ext cx="526805" cy="211718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S3-S1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>71710</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>79829</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>598515</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>101047</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="142" name="TextBox 141">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1326270D-2061-4490-B7C0-EB4166EA72C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8751884" y="6366329"/>
+          <a:ext cx="526805" cy="211718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S3-S1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>99870</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>50012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>13762</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>71230</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="143" name="TextBox 142">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D27AF29B-BEAF-4E0A-8BDB-ABD7B38CD751}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8780044" y="6908012"/>
+          <a:ext cx="526805" cy="211718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S3-S3</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>144596</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>119586</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>58488</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>140804</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="144" name="TextBox 143">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDCB9C0F-7D5D-4253-930F-CDB14C0B2C0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10050596" y="6406086"/>
+          <a:ext cx="526805" cy="211718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S1-S1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>156192</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>73203</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>70084</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>94421</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="145" name="TextBox 144">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{547A0D4B-5F1F-42D0-88E7-C6FFF2B92E5E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10062192" y="6931203"/>
+          <a:ext cx="526805" cy="211718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S1-S3</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>176070</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>93082</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>89962</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="146" name="TextBox 145">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C43561E8-B40B-44B8-A3C0-8D1DBFB148D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10694983" y="6951082"/>
+          <a:ext cx="526805" cy="211718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1000" b="1"/>
+            <a:t>S1-S3</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>25669</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>128055</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>372382</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>116470</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="147" name="Group 146">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B199D6D6-A4C5-448B-9EA2-00A5462C230D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6254191" y="2985555"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="148" name="Straight Connector 147">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E2B4113-AC2B-97AF-1FF2-A2680C22D1D3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="149" name="Straight Connector 148">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCDBF88D-A857-1118-7067-664CC25747E9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>56316</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>103206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>403029</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>91621</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="150" name="Group 149">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5B2AA4D-AEE5-47EE-B9B3-20F55ED01A76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6284838" y="3532206"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="151" name="Straight Connector 150">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{708998E1-2924-6A56-CF93-CB24F4259754}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="152" name="Straight Connector 151">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77117B56-BDDE-825B-CBE1-880DB7FC6E7A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>125889</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>81672</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>472602</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>70087</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="153" name="Group 152">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EC39311-1B77-4B2F-9916-6A5F9D37CD0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6967324" y="3510672"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="154" name="Straight Connector 153">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22D131E7-470D-226B-F516-7AF5746B2D10}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="155" name="Straight Connector 154">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DBC2312-F5C7-DDD9-E8A4-93E207D13352}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38094</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>76701</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>384807</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>65118</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="156" name="Group 155">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2283653A-39F8-4403-8EE8-92F97735BB9B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6266616" y="5220201"/>
+          <a:ext cx="346713" cy="369417"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358531"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="157" name="Straight Connector 156">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11963A23-31DF-0B39-0F62-18E3E9C5A779}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="158" name="Straight Connector 157">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B3B1C32-7D77-7E34-7FDF-977F0C2AF634}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648604"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38094</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>76701</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>384807</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>65116</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="159" name="Group 158">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4428362F-34B6-435F-ABDF-46DC9D1D8B49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6266616" y="5220201"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="160" name="Straight Connector 159">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A144BF7D-BDB7-70DA-4437-8B624DF8C4D7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="161" name="Straight Connector 160">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4D2BB81-2415-1F00-2486-92BF8C79D3F8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>82821</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>38601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>429534</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>27016</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="162" name="Group 161">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F8AF20B-1A2E-478C-852B-60A1A8D6954E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="7537169" y="5182101"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="163" name="Straight Connector 162">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89163E4D-4B6E-1718-DCA1-F5B470341D91}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="164" name="Straight Connector 163">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{618421B8-E760-1FD8-F892-A86B3D2F0554}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>182218</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>24849</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>528931</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>13264</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="168" name="Group 167">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A72D912A-585F-432E-B23E-DA17967C1FDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="8249479" y="4596849"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="169" name="Straight Connector 168">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44C6A39B-3962-C9ED-D6DE-B5B080DFEE46}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="170" name="Straight Connector 169">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8257AF66-BCA4-8C94-0D87-460C7BF54C2D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>185531</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>19880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>532244</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>8295</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="171" name="Group 170">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48C4F86B-7FD6-45A8-A569-EDF406D98C1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="8252792" y="6877880"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="172" name="Straight Connector 171">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F3476BF-1AFE-7EF5-2D8A-C2126E22FCC6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="173" name="Straight Connector 172">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6D412A4-3AC4-A7B0-F632-BE342C0AEA2D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>139148</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>139150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>485861</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>127565</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="174" name="Group 173">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66DBB296-28AF-42A1-889E-418F233BF891}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="8819322" y="6235150"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="175" name="Straight Connector 174">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D59A304-0DAF-BE76-EE25-66A2C5C1C637}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="176" name="Straight Connector 175">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D23F4DF2-8592-A662-EDFE-A5C65DFA43B6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>101048</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>26507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>447761</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>14922</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="177" name="Group 176">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{760CDA48-34B3-42C5-974D-1CF54F62DC37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="8781222" y="5741507"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="178" name="Straight Connector 177">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3A0D3E0-2E6B-546A-4795-FD86E0285225}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="179" name="Straight Connector 178">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BCC15E6-F62C-AAE5-3274-AA0EC5EFEFA0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>220317</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>21537</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>567030</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>9952</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="180" name="Group 179">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE3D0217-5976-4B07-8014-78F162CCDD24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10126317" y="6879537"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="181" name="Straight Connector 180">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06BD54F3-F999-5D61-F502-887F76433372}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="182" name="Straight Connector 181">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB2469E4-C900-8636-69FA-7945704A4878}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1" flipV="1">
+            <a:off x="1199213" y="2648602"/>
+            <a:ext cx="346713" cy="338554"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>215348</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>16567</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>562061</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>4982</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="183" name="Group 182">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ADDCE20-95A0-4C09-9E84-49A88293BCD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10734261" y="6874567"/>
+          <a:ext cx="346713" cy="369415"/>
+          <a:chOff x="1199213" y="2628627"/>
+          <a:chExt cx="346713" cy="358529"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="184" name="Straight Connector 183">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{450207D4-2703-A400-89DC-ABB32E102410}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1214203" y="2628627"/>
+            <a:ext cx="299803" cy="351034"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="19050"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="185" name="Straight Connector 184">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C300869-CB75-6A9D-E800-CABE1FA559BD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3330,17 +7767,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AFBD0E2-CBFE-4CB4-BDEE-CE5AA6A4EB61}">
   <dimension ref="B2:M27"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.69140625" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>17</v>
       </c>
@@ -3354,7 +7791,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="9"/>
       <c r="C4" s="3" t="s">
         <v>0</v>
@@ -3372,7 +7809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
@@ -3392,7 +7829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
@@ -3412,7 +7849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
@@ -3432,7 +7869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
@@ -3452,7 +7889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
@@ -3471,8 +7908,11 @@
       <c r="G9" s="2">
         <v>1</v>
       </c>
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3492,7 +7932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -3512,7 +7952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -3532,7 +7972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
@@ -3552,7 +7992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -3560,17 +8000,17 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="M15" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>17</v>
       </c>
@@ -3584,7 +8024,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
       <c r="C18" s="3" t="s">
         <v>0</v>
@@ -3602,47 +8042,107 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -3650,7 +8150,7 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -3658,7 +8158,7 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -3666,7 +8166,7 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -3690,9 +8190,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231B1F40-B803-4D30-B81D-67449ED4D5CD}">
   <dimension ref="A4:C6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="1:3" ht="35.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="35.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
         <v>6</v>
@@ -3701,8 +8201,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="39.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="1:3" ht="41.6" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:3" ht="41.65" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
